--- a/angle_final_ready_for_upload.xlsx
+++ b/angle_final_ready_for_upload.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P107"/>
+  <dimension ref="A1:P93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,12 +537,12 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
         <is>
           <t>https://openstax.org/books/precalculus-2e/pages/7-3-double-angle-half-angle-and-reduction-formulas</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -561,18 +561,18 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$$sin(2θ)$$</t>
+          <t>Evaluate $$sin(2θ)$$</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-24/25</t>
+          <t>$$- \frac{24}{25}$$</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>algebraic</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -599,12 +599,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Double-Angle Formula for Sine</t>
+          <t>Double-angle formula for sine</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Recall that $$sin(2θ) = 2sin(θ)cos(θ)$$.</t>
+          <t>Recall that $$sin(2θ) = 2sin(θ)cos(θ)$$</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -637,22 +637,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Determine sin(θ)</t>
+          <t>Find sin(θ)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Given $$tanθ=−\frac{3}{4}$$ and $$θ$$ is in quadrant II, what is the value of $$sin(θ)$$?</t>
+          <t>Given $$tanθ=−\frac{3}{4}$$ and $$θ$$ is in quadrant II, what is $$sin(θ)$$?</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>$$3/5$$</t>
+          <t>$$\frac{3}{5}$$</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>algebraic</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Determine cos(θ)</t>
+          <t>Find cos(θ)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>You'll also need $$cos(θ)$$. Remember the relationship between tangent, sine, and cosine, and the quadrant.</t>
+          <t>Use the Pythagorean identity or a right triangle to find $$cos(θ)$$</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -729,22 +729,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Determine cos(θ)</t>
+          <t>Find cos(θ)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Given $$tanθ=−\frac{3}{4}$$ and $$θ$$ is in quadrant II, what is the value of $$cos(θ)$$?</t>
+          <t>Given $$tanθ=−\frac{3}{4}$$ and $$θ$$ is in quadrant II, what is $$cos(θ)$$?</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>$$-4/5$$</t>
+          <t>$$-\frac{4}{5}$$</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>algebraic</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -774,31 +774,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Calculate sin(2θ)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Now substitute the values of $$sin(θ)$$ and $$cos(θ)$$ into the double-angle formula for sine.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>Evaluate $$cos(2θ)$$</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>$$- \frac{7}{25}$$</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -816,39 +812,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Final Calculation</t>
+          <t>Double-angle formula for cosine</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>What is $$2 \cdot (\frac{3}{5}) \cdot (-\frac{4}{5})$$?</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>$$-24/25$$</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
+          <t>Recall that $$cos(2θ) = cos^2(θ) - sin^2(θ)$$ (or other forms)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -866,27 +850,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>$$cos(2θ)$$</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Apply the formula</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Substitute the values of $$sin(θ)$$ and $$cos(θ)$$ into the formula. What is $$cos^2(θ) - sin^2(θ)$$?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>$$\frac{7}{25}$$</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -904,26 +900,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Double-Angle Formula for Cosine</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Recall that $$cos(2θ)$$ has three forms: $$cos^2(θ) - sin^2(θ)$$, $$1 - 2sin^2(θ)$$, or $$2cos^2(θ) - 1$$.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+          <t>Evaluate $$tan(2θ)$$</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>$$- \frac{24}{7}$$</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -942,39 +938,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Select a Formula</t>
+          <t>Double-angle formula for tangent</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Which form of the double-angle formula for cosine would be easiest to use given you know $$sin(θ)$$ and $$cos(θ)$$?</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>$$cos^2(θ) - sin^2(θ)$$</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
+          <t>Recall that $$tan(2θ) = \frac{2tan(θ)}{1 - tan^2(θ)}$$</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>s1</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
           <t>h1</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -992,24 +976,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Substitute and Calculate</t>
+          <t>Substitute tan(θ)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Substitute the values of $$sin(θ)$$ and $$cos(θ)$$ into your chosen formula.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+          <t>Substitute $$tanθ=−\frac{3}{4}$$ into the formula. What is the value of the numerator?</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>$$-\frac{3}{2}$$</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>s1</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1034,37 +1026,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Final Calculation</t>
+          <t>Alternative formula for tangent</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Using $$sin(θ) = \frac{3}{5}$$ and $$cos(θ) = -\frac{4}{5}$$, what is $$cos(2θ)$$?</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>$$7/25$$</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
+          <t>Alternatively, you can use $$tan(2θ) = \frac{sin(2θ)}{cos(2θ)}$$ from the previous steps.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>h1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1084,27 +1068,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>$$tan(2θ)$$</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Calculate the denominator</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Using the formula $$tan(2θ) = \frac{2tan(θ)}{1 - tan^2(θ)}$$, what is the value of the denominator $$1 - tan^2(θ)$$?</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-24/7</t>
+          <t>$$\frac{7}{16}$$</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1117,36 +1113,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>angle1</t>
+          <t>angle2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Double-Angle Formula for Tangent</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Recall that $$tan(2θ) = \frac{2tan(θ)}{1 - tan^2(θ)}$$. Alternatively, you can use $$tan(2θ) = \frac{sin(2θ)}{cos(2θ)}$$.</t>
-        </is>
-      </c>
+          <t>Using the Double-Angle Formula for Cosine without Exact Values</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-3-double-angle-half-angle-and-reduction-formulas</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -1155,36 +1147,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>angle1</t>
+          <t>angle2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Substitute and Calculate</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Substitute the value of $$tan(θ)$$ into the formula.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+          <t>Use the double-angle formula for cosine to write $$cos(6x)$$ in terms of $$cos(3x).$$</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>$$2cos^2(3x) - 1$$</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1197,44 +1185,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>angle1</t>
+          <t>angle2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Final Calculation</t>
+          <t>Double-angle formula for cosine</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Using $$tanθ=−\frac{3}{4}$$, what is $$tan(2θ)$$?</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>$$-24/7$$</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
+          <t>Recall one of the double-angle formulas for cosine: $$cos(2A) = 2cos^2(A) - 1$$</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1245,14 +1221,46 @@
       <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>angle2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>scaffold</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Identify A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>If we want to express $$cos(6x)$$ as $$cos(2A)$$, what should $$A$$ be in terms of $$x$$?</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>$$3x$$</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1270,27 +1278,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Using the Double-Angle Formula for Cosine without Exact Values</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Substitute into the formula</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Once you've identified $$A$$, substitute it into the chosen double-angle formula.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-3-double-angle-half-angle-and-reduction-formulas</t>
-        </is>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1304,15 +1320,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Use the double-angle formula for cosine to write $$cos(6x)$$ in terms of $$cos(3x).$$</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Perform the substitution</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Substitute $$A=3x$$ into $$cos(2A) = 2cos^2(A) - 1$$. What is the resulting expression?</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>$$2cos^2(3x) - 1$$</t>
@@ -1323,8 +1343,16 @@
           <t>algebraic</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1337,36 +1365,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>angle2</t>
+          <t>angle3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Double-Angle Formula for Cosine</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Recall one of the double-angle formulas for cosine: $$cos(2A) = 2cos^2(A) - 1$$.</t>
-        </is>
-      </c>
+          <t>Using the Double-Angle Formulas to Establish an Identity</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-3-double-angle-half-angle-and-reduction-formulas</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1375,27 +1399,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>angle2</t>
+          <t>angle3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Identify A</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>If we want to express $$cos(6x)$$ in terms of $$cos(3x)$$, what should $$A$$ be in the formula $$cos(2A)$$?</t>
-        </is>
-      </c>
+          <t>Evaluate the expression $$(sinθ+cosθ)^{2}$$</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>$$3x$$</t>
+          <t>$$1+sin(2θ)$$</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1403,16 +1423,8 @@
           <t>algebraic</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>s1</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1425,7 +1437,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>angle2</t>
+          <t>angle3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1435,26 +1447,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Substitute and Simplify</t>
+          <t>Expand the right side</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Substitute $$A = 3x$$ into the chosen double-angle formula.</t>
+          <t>Start by expanding the right side of the identity, $$(sinθ+cosθ)^{2}$$</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
           <t>h1</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1467,7 +1475,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>angle2</t>
+          <t>angle3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1477,17 +1485,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Final Expression</t>
+          <t>Expand the binomial</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Substitute $$A = 3x$$ into $$2cos^2(A) - 1$$ to get the expression for $$cos(6x)$$.</t>
+          <t>What is the result of expanding $$(sinθ+cosθ)^{2}$$?</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>$$2cos^2(3x) - 1$$</t>
+          <t>$$sin^2(θ) + 2sin(θ)cos(θ) + cos^2(θ)$$</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1497,12 +1505,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>s1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>h1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1515,14 +1523,38 @@
       <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>angle3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply identities</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Look for trigonometric identities that can simplify the expanded expression.</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1540,27 +1572,43 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Using the Double-Angle Formulas to Establish an Identity</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+          <t>Use Pythagorean Identity</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>What is $$sin^2(θ) + cos^2(θ)$$ equal to?</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>$$1$$</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-3-double-angle-half-angle-and-reduction-formulas</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -1574,27 +1622,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Evaluate the expression $$(sinθ+cosθ)^{2}$$ and show it is equal to $$1+sin(2θ)$$.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>$$1+sin(2θ)$$</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+          <t>Apply double-angle formula</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Identify the double-angle formula for sine in the remaining terms.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1612,27 +1664,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Choose a Side to Start</t>
+          <t>Use Double-Angle Formula for Sine</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>It's often easier to start with the more complex side of an identity and simplify it. Which side is more complex?</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+          <t>What is $$2sin(θ)cos(θ)$$ equal to?</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>$$sin(2θ)$$</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1645,44 +1709,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>angle3</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Identify Complex Side</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Which side of the identity $$1+sin(2θ)=(sinθ+cosθ)^{2}$$ is generally considered more complex to work with?</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Right-hand side (RHS)</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>s1</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+          <t>angle4,problem,Verifying a Double-Angle Identity for Tangent,,,,,,,,,https://openstax.org/books/precalculus-2e/pages/7-3-double-angle-half-angle-and-reduction-formulas,,,,</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1695,36 +1731,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>angle3</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Expand the Expression</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Expand the expression $$(sinθ+cosθ)^{2}$$. Remember the formula $$(a+b)^2 = a^2 + 2ab + b^2$$.</t>
-        </is>
-      </c>
+          <t>angle4,step,Show that the right side of the identity, $$\frac{2}{cotθ−tanθ}$$, simplifies to $$tan(2\theta)$$,,$$tan(2\theta)$$,algebra,,,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1737,44 +1753,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>angle3</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Expand RHS</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Expand $$(sinθ+cosθ)^{2}$$.</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>$$sin^2(θ) + 2sin(θ)cos(θ) + cos^2(θ)$$</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>angle4,hint,Recall definitions of cotangent and tangent,"To simplify the expression, it's often helpful to rewrite trigonometric functions in terms of sine and cosine.",,,h1,,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -1787,36 +1775,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>angle3</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Apply Identities</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Look for Pythagorean identities and double-angle formulas within the expanded expression.</t>
-        </is>
-      </c>
+          <t>angle4,scaffold,Rewrite in terms of sine and cosine,"What is $$cot\theta$$ and $$tan\theta$$ in terms of $$sin\theta$$ and $$cos\theta$$?",$$cot\theta = \frac{cos\theta}{sin\theta}$$, $$tan\theta = \frac{sin\theta}{cos\theta}$$,algebra,h2,h1,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -1829,44 +1797,16 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>angle3</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Simplify to LHS</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Simplify $$sin^2(θ) + 2sin(θ)cos(θ) + cos^2(θ)$$ using the Pythagorean identity and the double-angle formula for sine.</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>$$1+sin(2θ)$$</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+          <t>angle4,hint,Simplify the complex fraction,"Combine the terms in the denominator by finding a common denominator.",,,h1,,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -1877,7 +1817,11 @@
       <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>angle4,scaffold,Combine denominator terms,"What is the common denominator for $$\frac{cos\theta}{sin\theta} - \frac{sin\theta}{cos\theta}$$?",$$sin\theta cos\theta$$,algebra,h2,h1,,,,,,,,</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -1897,19 +1841,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>angle4</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>problem</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Verifying a Double-Angle Identity for Tangent</t>
-        </is>
-      </c>
+          <t>angle4,hint,Apply double-angle identity,"After simplifying the fraction, look for a form that matches a double-angle identity for tangent.",,,h1,,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
@@ -1918,11 +1854,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-3-double-angle-half-angle-and-reduction-formulas</t>
-        </is>
-      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -1931,30 +1863,14 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>angle4</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Evaluate the expression: $$\frac{2}{cotθ−tanθ}$$</t>
-        </is>
-      </c>
+          <t>angle4,scaffold,Recognize the double-angle identity,"The simplified expression should be $$\frac{2sin\theta cos\theta}{cos^2\theta - sin^2\theta}$$. Which double-angle identity for tangent does this match?",$$tan(2\theta)$$,algebra,h2,h1,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>$$tan(2θ)$$</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -1969,31 +1885,15 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>angle4</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Rewrite cotangent</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Recall that $$cotθ = \frac{1}{tanθ}$$</t>
-        </is>
-      </c>
+          <t>,,,,,,,,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
@@ -2007,44 +1907,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>angle4</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Rewrite the denominator in terms of tangent</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>What is $$cotθ - tanθ$$ in terms of $$tanθ$$?</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>$$\frac{1}{tanθ} - tanθ$$</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>s1</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+          <t>angle5,problem,Writing an Equivalent Expression Not Containing Powers Greater Than 1,,,,,,,,,https://openstax.org/books/precalculus-2e/pages/7-3-double-angle-half-angle-and-reduction-formulas,,,,</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2057,36 +1929,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>angle4</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Simplify the denominator</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Combine the terms in the denominator into a single fraction.</t>
-        </is>
-      </c>
+          <t>angle5,step,Write an equivalent expression for $$cos^{4}x$$ that does not involve any powers of sine or cosine greater than 1.,,$$\frac{3}{8} + \frac{1}{2}cos(2x) + \frac{1}{8}cos(4x)$$,algebra,,,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -2099,44 +1951,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>angle4</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Simplify the expression for the denominator</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>What is the simplified form of `$$\frac{1}{tanθ} - tanθ$$`?</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>$$\frac{1-tan^2θ}{tanθ}$$</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>angle5,hint,Use power-reducing formula for cosine squared,"Recall the power-reducing formula for $$cos^2\theta$$.",,,h1,,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2149,36 +1973,16 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>angle4</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Simplify the complex fraction</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Substitute the simplified denominator back into the original expression and simplify the complex fraction.</t>
-        </is>
-      </c>
+          <t>angle5,scaffold,Apply first power-reducing formula,"Rewrite $$cos^4x$$ as $$(cos^2x)^2$$ and apply the power-reducing formula for $$cos^2x$$. What is the result?",$$(\frac{1+cos(2x)}{2})^2$$,algebra,h2,h1,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2191,44 +1995,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>angle4</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Simplify the complex fraction</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>What is the simplified form of `$$\frac{2}{\frac{1-tan^2θ}{tanθ}}$$`?</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>$$\frac{2tanθ}{1-tan^2θ}$$</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+          <t>angle5,hint,Expand and simplify,"Expand the squared term and simplify. You may encounter another squared trigonometric term.",,,h1,,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2241,36 +2017,16 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>angle4</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Recognize the identity</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Compare your simplified expression to the double-angle identity for tangent.</t>
-        </is>
-      </c>
+          <t>angle5,scaffold,Identify remaining squared term,"Expand $$(\frac{1+cos(2x)}{2})^2$$. What term still has a power greater than 1?",$$cos^2(2x)$$,algebra,h2,h1,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>h4</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -2283,44 +2039,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>angle4</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Recognize the identity</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>What double-angle identity does `$$\frac{2tanθ}{1-tan^2θ}$$` represent?</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>$$tan(2θ)$$</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>s4</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>h4</t>
-        </is>
-      </c>
+          <t>angle5,hint,Apply power-reducing formula again,"Apply the power-reducing formula to the remaining squared term, remembering to adjust the angle.",,,h1,,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2331,7 +2059,11 @@
       <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>angle5,scaffold,Apply second power-reducing formula,"Apply the power-reducing formula to $$cos^2(2x)$$. What is the result?",$$\frac{1+cos(4x)}{2}$$,algebra,h2,h1,,,,,,,,</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
@@ -2351,19 +2083,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>angle5</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>problem</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Writing an Equivalent Expression Not Containing Powers Greater Than 1</t>
-        </is>
-      </c>
+          <t>,,,,,,,,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
@@ -2372,11 +2096,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-3-double-angle-half-angle-and-reduction-formulas</t>
-        </is>
-      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
@@ -2385,30 +2105,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>angle5</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Write an equivalent expression for $$cos^{4}x$$ that does not involve any powers of sine or cosine greater than 1.</t>
-        </is>
-      </c>
+          <t>angle6,problem,Using the Power-Reducing Formulas to Prove an Identity,,,,,,,,,https://openstax.org/books/precalculus-2e/pages/7-3-double-angle-half-angle-and-reduction-formulas,,,,</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>$$\frac{3}{8} + \frac{1}{2}cos(2x) + \frac{1}{8}cos(4x)$$</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -2423,31 +2127,15 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>angle5</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Use Power-Reducing Formula for $$cos^2x$$</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Recall that $$cos^2x = \frac{1+cos(2x)}{2}$$</t>
-        </is>
-      </c>
+          <t>angle6,step,Show that $$sin^{3}(2x)$$ simplifies to $$[\frac{1}{2}sin(2x)][1−cos(4x)]$$ using power-reducing formulas.,, $$[\frac{1}{2}sin(2x)][1−cos(4x)]$$,algebra,,,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
@@ -2461,44 +2149,16 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>angle5</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Rewrite $$cos^4x$$ using the power-reducing formula</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>How can you express $$cos^4x$$ using the formula for $$cos^2x$$?</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>$$(\frac{1+cos(2x)}{2})^2$$</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>s1</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+          <t>angle6,hint,Break down the cubic term,"Rewrite $$sin^3(2x)$$ to isolate a squared term that can use a power-reducing formula.",,,h1,,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -2511,36 +2171,16 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>angle5</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Expand and apply formula again</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Expand the squared expression. You will need to apply the power-reducing formula again to any squared cosine terms, remembering to adjust the angle.</t>
-        </is>
-      </c>
+          <t>angle6,scaffold,Factor the cubic term,"How can you rewrite $$sin^3(2x)$$ to prepare for a power-reducing formula?",$$sin(2x) \cdot sin^2(2x)$$,algebra,h2,h1,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2553,44 +2193,16 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>angle5</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Expand the expression and apply the power-reducing formula to $$cos^2(2x)$$</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>What is the expanded form of `$$(\frac{1+cos(2x)}{2})^2$$` after applying the power-reducing formula to $$cos^2(2x)$$?</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>$$\frac{1+2cos(2x)+\frac{1+cos(4x)}{2}}{4}$$</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>angle6,hint,Apply power-reducing formula for sine squared,"Recall and apply the power-reducing formula for $$sin^2\theta$$.",,,h1,,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -2603,36 +2215,16 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>angle5</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Simplify the expression</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Combine all terms and simplify the fraction to get the final expression.</t>
-        </is>
-      </c>
+          <t>angle6,scaffold,Apply power-reducing formula,"What is the power-reducing formula for $$sin^2(2x)$$?",$$\frac{1-cos(4x)}{2}$$,algebra,h2,h1,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -2645,44 +2237,16 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>angle5</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Simplify the entire expression</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>What is the fully simplified expression?</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>$$\frac{3}{8} + \frac{1}{2}cos(2x) + \frac{1}{8}cos(4x)$$</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+          <t>angle6,hint,Combine and simplify,"Substitute the power-reduced term back into the expression and simplify to match the target identity.",,,h1,,,,,,,,,</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -2693,7 +2257,11 @@
       <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>angle6,scaffold,Substitute and simplify,"Substitute $$\frac{1-cos(4x)}{2}$$ for $$sin^2(2x)$$ into $$sin(2x) \cdot sin^2(2x)$$. What is the resulting expression?",$$sin(2x) \cdot \frac{1-cos(4x)}{2}$$,algebra,h2,h1,,,,,,,,</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
@@ -2713,7 +2281,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>angle6</t>
+          <t>angle7</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2723,7 +2291,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Using the Power-Reducing Formulas to Prove an Identity</t>
+          <t>Using a Half-Angle Formula to Find the Exact Value of a Sine Function</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -2747,7 +2315,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>angle6</t>
+          <t>angle7</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2757,18 +2325,18 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Write an equivalent expression for $$sin^3(2x)$$ using power-reducing formulas.</t>
+          <t>Find $$sin(15^{∘})$$ using a half-angle formula.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>$$[\frac{1}{2}sin(2x)][1−cos(4x)]$$</t>
+          <t>$$\frac{\sqrt{2-\sqrt{3}}}{2}$$</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>algebraic</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -2785,7 +2353,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>angle6</t>
+          <t>angle7</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2795,12 +2363,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rewrite $$sin^3(2x)$$</t>
+          <t>Recall Half-Angle Formula</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Break down $$sin^3(2x)$$ into a product involving $$sin^2(2x)$$.</t>
+          <t>The half-angle formula for sine is `$$\sin\left(\frac{\alpha}{2}\right) = \pm\sqrt{\frac{1-\cos\alpha}{2}}$$`.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2823,7 +2391,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>angle6</t>
+          <t>angle7</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2833,22 +2401,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rewrite $$sin^3(2x)$$ to prepare for power-reducing formulas</t>
+          <t>Identify `$$\alpha$$`</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Rewrite $$sin^3(2x)$$ as a product of a sine term and a squared sine term.</t>
+          <t>If `$$\frac{\alpha}{2} = 15^\circ$$`, what is `$$\alpha$$`?</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>$$sin(2x) \cdot sin^2(2x)$$</t>
+          <t>$$30^\circ$$</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>algebraic</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2873,7 +2441,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>angle6</t>
+          <t>angle7</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2883,12 +2451,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Apply Power-Reducing Formula for Sine Squared</t>
+          <t>Determine the Sign</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Recall that $$sin^2A = \frac{1-cos(2A)}{2}$$. Apply this to $$sin^2(2x)$$.</t>
+          <t>Since `$$15^\circ$$` is in Quadrant I, `$$\sin(15^\circ)$$` will be positive.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2915,7 +2483,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>angle6</t>
+          <t>angle7</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2925,22 +2493,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Apply the power-reducing formula to $$sin^2(2x)$$</t>
+          <t>Find `$$\cos(\alpha)$$`</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>What is $$sin^2(2x)$$ using the power-reducing formula?</t>
+          <t>What is the exact value of `$$\cos(30^\circ)$$`?</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>$$\frac{1-cos(4x)}{2}$$</t>
+          <t>$$\frac{\sqrt{3}}{2}$$</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>algebraic</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2965,7 +2533,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>angle6</t>
+          <t>angle7</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2975,12 +2543,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Substitute and simplify</t>
+          <t>Substitute and Simplify</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Substitute the result from the power-reducing formula back into your rewritten expression for $$sin^3(2x)$$ and simplify.</t>
+          <t>Substitute the value of `$$\cos(30^\circ)$$` into the formula and simplify the expression.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3007,7 +2575,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>angle6</t>
+          <t>angle7</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3017,22 +2585,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Substitute and simplify the expression</t>
+          <t>Substitute values</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Substitute `$$\frac{1-cos(4x)}{2}$$` for $$sin^2(2x)$$ in `$$sin(2x) \cdot sin^2(2x)$$` and simplify to match the target form.</t>
+          <t>Substitute `$$\cos(30^\circ) = \frac{\sqrt{3}}{2}$$` into `$$\sqrt{\frac{1-\cos(30^\circ)}{2}}$$`.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>$$[\frac{1}{2}sin(2x)][1−cos(4x)]$$</t>
+          <t>$$\sqrt{\frac{1-\frac{\sqrt{3}}{2}}{2}}$$`</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>algebraic</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3057,7 +2625,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>angle7</t>
+          <t>angle8</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3067,10 +2635,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Using a Half-Angle Formula to Find the Exact Value of a Sine Function</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Finding Exact Values Using Half-Angle Identities</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Given that $$tanα=\frac{8}{15}$$ and $$α$$ lies in quadrant III, find the exact value of the following:</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
@@ -3091,7 +2663,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>angle7</t>
+          <t>angle8</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3101,18 +2673,18 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Find $$sin(15^{∘})$$ using a half-angle formula.</t>
+          <t>$$sin(\frac{α}{2})$$</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{6}-\sqrt{2}}{4}$$</t>
+          <t>$$\frac{4\sqrt{17}}{17}$$</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -3129,7 +2701,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>angle7</t>
+          <t>angle8</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3139,12 +2711,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Recall the half-angle formula for sine.</t>
+          <t>Quadrant of Half-Angle</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Recall that $$\sin\left(\frac{\alpha}{2}\right) = \pm\sqrt{\frac{1-\cos\alpha}{2}}$$.</t>
+          <t>If `$$\alpha$$` is in Quadrant III (`$$180^\circ &lt; \alpha &lt; 270^\circ$$`), then `$$\frac{\alpha}{2}$$` will be in Quadrant II (`$$90^\circ &lt; \frac{\alpha}{2} &lt; 135^\circ$$`). This determines the sign of `$$\sin\left(\frac{\alpha}{2}\right)$$`.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -3167,7 +2739,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>angle7</t>
+          <t>angle8</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3177,22 +2749,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Identify the half-angle formula for sine.</t>
+          <t>Sign of Sine</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>What is the half-angle formula for sine?</t>
+          <t>Based on the quadrant of `$$\frac{\alpha}{2}$$`, will `$$\sin\left(\frac{\alpha}{2}\right)$$` be positive or negative?</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>$$\sin\left(\frac{\alpha}{2}\right) = \pm\sqrt{\frac{1-\cos\alpha}{2}}$$</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>algebraic</t>
+          <t>mc</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3205,7 +2777,11 @@
           <t>h1</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Positive|Negative</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
@@ -3217,7 +2793,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>angle7</t>
+          <t>angle8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3227,12 +2803,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Identify $$\alpha$$.</t>
+          <t>Find `$$\cos\alpha$$`</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>What angle $$\alpha$$ makes $$\frac{\alpha}{2} = 15^\circ$$?</t>
+          <t>You are given `$$\tan\alpha = \frac{8}{15}$$` and `$$\alpha$$` is in Quadrant III. Use this information to find `$$\cos\alpha$$`.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -3259,7 +2835,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>angle7</t>
+          <t>angle8</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3269,22 +2845,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>What is $$\alpha$$?</t>
+          <t>Calculate `$$\cos\alpha$$`</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>What is the value of $$\alpha$$?</t>
+          <t>Given `$$\tan\alpha = \frac{8}{15}$$` and `$$\alpha$$` in QIII, what is `$$\cos\alpha$$`?</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>$$30^\circ$$</t>
+          <t>$$-\frac{15}{17}$$</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3309,7 +2885,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>angle7</t>
+          <t>angle8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3319,12 +2895,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Determine the sign and value.</t>
+          <t>Apply Half-Angle Formula</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Since $$15^\circ$$ is in Quadrant I, $$\sin(15^\circ)$$ will be positive. Recall the value of $$\cos(30^\circ)$$.</t>
+          <t>Use the formula `$$\sin\left(\frac{\alpha}{2}\right) = \pm\sqrt{\frac{1-\cos\alpha}{2}}$$` with the correct sign and the value of `$$\cos\alpha$$`.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -3351,7 +2927,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>angle7</t>
+          <t>angle8</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3361,22 +2937,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>What is $$\cos(30^\circ)$$?</t>
+          <t>Substitute and Simplify</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>What is the exact value of $$\cos(30^\circ)$$?</t>
+          <t>Substitute `$$\cos\alpha = -\frac{15}{17}$$` into the half-angle formula and simplify.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{3}}{2}$$</t>
+          <t>$$\sqrt{\frac{1-(-\frac{15}{17})}{2}}$$`</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3401,44 +2977,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>angle7</t>
+          <t>angle8</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Substitute and simplify.</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Substitute $$\cos(30^\circ)$$ into the formula and simplify.</t>
-        </is>
-      </c>
+          <t>$$cos(\frac{α}{2})$$</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{6}-\sqrt{2}}{4}$$</t>
+          <t>$$-\frac{\sqrt{17}}{17}$$</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>s4</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+          <t>algebra</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3456,26 +3020,26 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>$$sin(\frac{α}{2})$$</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>$$\frac{4\sqrt{17}}{17}$$</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
+          <t>Quadrant of Half-Angle</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>As established, `$$\frac{\alpha}{2}$$` is in Quadrant II. This determines the sign of `$$\cos\left(\frac{\alpha}{2}\right)$$`.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
@@ -3494,28 +3058,44 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Recall the half-angle formula for sine.</t>
+          <t>Sign of Cosine</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Recall that $$\sin\left(\frac{\alpha}{2}\right) = \pm\sqrt{\frac{1-\cos\alpha}{2}}$$.</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+          <t>Based on the quadrant of `$$\frac{\alpha}{2}$$`, will `$$\cos\left(\frac{\alpha}{2}\right)$$` be positive or negative?</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>mc</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
           <t>h1</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Positive|Negative</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
@@ -3532,32 +3112,24 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>What is the half-angle formula for sine?</t>
+          <t>Recall `$$\cos\alpha$$`</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>What is the half-angle formula for sine?</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>$$\sin\left(\frac{\alpha}{2}\right) = \pm\sqrt{\frac{1-\cos\alpha}{2}}$$</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
+          <t>From the previous step, we found `$$\cos\alpha = -\frac{15}{17}$$`.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3582,29 +3154,37 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Determine $$\cos\alpha$$.</t>
+          <t>Value of `$$\cos\alpha$$`</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Use the given $$\tan\alpha$$ and quadrant information to find $$\cos\alpha$$.</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
+          <t>What is the value of `$$\cos\alpha$$`?</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>$$-\frac{15}{17}$$</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
           <t>h2</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>h1</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -3624,32 +3204,24 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>What is $$\cos\alpha$$?</t>
+          <t>Apply Half-Angle Formula</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Given $$\tan\alpha=\frac{8}{15}$$ and $$\alpha$$ is in QIII, what is $$\cos\alpha$$?</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>$$-\frac{15}{17}$$</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
+          <t>Use the formula `$$\cos\left(\frac{\alpha}{2}\right) = \pm\sqrt{\frac{1+\cos\alpha}{2}}$$` with the correct sign and the value of `$$\cos\alpha$$`.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>h3</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3674,29 +3246,37 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Determine the sign of $$\sin(\frac{\alpha}{2})$$.</t>
+          <t>Substitute and Simplify</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Since $$\alpha$$ is in QIII ($$180^\circ &lt; \alpha &lt; 270^\circ$$), what quadrant is $$\frac{\alpha}{2}$$ in? This will determine the sign of $$\sin(\frac{\alpha}{2})$$.</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+          <t>Substitute `$$\cos\alpha = -\frac{15}{17}$$` into the half-angle formula and simplify.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>$$-\sqrt{\frac{1+(-\frac{15}{17})}{2}}$$`</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
           <t>h3</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>h2</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -3716,44 +3296,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>What quadrant is $$\frac{\alpha}{2}$$ in?</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>If $$\alpha$$ is in QIII, what quadrant is $$\frac{\alpha}{2}$$ in?</t>
-        </is>
-      </c>
+          <t>$$tan(\frac{α}{2})$$</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Quadrant II</t>
+          <t>$$-4$$</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>mc</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Quadrant I|Quadrant II|Quadrant III|Quadrant IV</t>
-        </is>
-      </c>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
@@ -3770,39 +3334,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Substitute and simplify.</t>
+          <t>Tangent as Ratio</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Substitute $$\cos\alpha$$ into the formula and simplify, choosing the correct sign.</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>$$\frac{4\sqrt{17}}{17}$$</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
+          <t>You have already calculated `$$\sin\left(\frac{\alpha}{2}\right)$$` and `$$\cos\left(\frac{\alpha}{2}\right)$$`. Use these values to find `$$\tan\left(\frac{\alpha}{2}\right)$$`.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>s4</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -3820,27 +3372,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>$$cos(\frac{α}{2})$$</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>Recall Sine and Cosine</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>What are the exact values you found for `$$\sin\left(\frac{\alpha}{2}\right)$$` and `$$\cos\left(\frac{\alpha}{2}\right)$$`?</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>$$-\frac{\sqrt{17}}{17}$$</t>
+          <t>$$\sin\left(\frac{\alpha}{2}\right) = \frac{4\sqrt{17}}{17}, \cos\left(\frac{\alpha}{2}\right) = -\frac{\sqrt{17}}{17}$$</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+          <t>algebra</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -3863,22 +3427,26 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Recall the half-angle formula for cosine.</t>
+          <t>Alternative Tangent Formula</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Recall that $$\cos\left(\frac{\alpha}{2}\right) = \pm\sqrt{\frac{1+\cos\alpha}{2}}$$.</t>
+          <t>You can also use `$$\tan\left(\frac{\alpha}{2}\right) = \frac{1-\cos\alpha}{\sin\alpha}$$`. You will need to find `$$\sin\alpha$$` first.</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
           <t>h1</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -3901,32 +3469,32 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>What is the half-angle formula for cosine?</t>
+          <t>Find `$$\sin\alpha$$`</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>What is the half-angle formula for cosine?</t>
+          <t>Given `$$\tan\alpha = \frac{8}{15}$$` and `$$\alpha$$` in QIII, what is `$$\sin\alpha$$`?</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>$$\cos\left(\frac{\alpha}{2}\right) = \pm\sqrt{\frac{1+\cos\alpha}{2}}$$</t>
+          <t>$$-\frac{8}{17}$$</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>algebraic</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>h1</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -3951,24 +3519,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Determine $$\cos\alpha$$.</t>
+          <t>Substitute and Simplify</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Use the given $$\tan\alpha$$ and quadrant information to find $$\cos\alpha$$.</t>
+          <t>Substitute the values of `$$\sin\alpha$$` and `$$\cos\alpha$$` into the tangent half-angle formula.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
           <t>h2</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>h1</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -3993,32 +3561,32 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>What is $$\cos\alpha$$?</t>
+          <t>Substitute values</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Given $$\tan\alpha=\frac{8}{15}$$ and $$\alpha$$ is in QIII, what is $$\cos\alpha$$?</t>
+          <t>Substitute `$$\cos\alpha = -\frac{15}{17}$$` and `$$\sin\alpha = -\frac{8}{17}$$` into `$$\frac{1-\cos\alpha}{\sin\alpha}$$`.</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>$$-\frac{15}{17}$$</t>
+          <t>$$\frac{1-(-\frac{15}{17})}{-\frac{8}{17}}$$`</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>s3</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>h3</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -4033,40 +3601,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>angle8</t>
+          <t>angle9</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Determine the sign of $$\cos(\frac{\alpha}{2})$$.</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Since $$\alpha/2$$ is in Quadrant II, $$\cos(\frac{\alpha}{2})$$ will be negative.</t>
-        </is>
-      </c>
+          <t>Finding the Measurement of a Half Angle</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-3-double-angle-half-angle-and-reduction-formulas</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -4075,49 +3635,33 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>angle8</t>
+          <t>angle9</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>What quadrant is $$\frac{\alpha}{2}$$ in?</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>If $$\alpha$$ is in QIII, what quadrant is $$\frac{\alpha}{2}$$ in?</t>
-        </is>
-      </c>
+          <t>Now, we will return to the problem posed at the beginning of the section. A bicycle ramp is constructed for high-level competition with an angle of $$θ$$ formed by the ramp and the ground. Another ramp is to be constructed half as steep for novice competition. If $$tanθ=\frac{5}{3}$$ for higher-level competition, what is the measurement of the angle for novice competition?</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Quadrant II</t>
+          <t>$$\arctan\left(\frac{\sqrt{34}-3}{5}\right)$$</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>mc</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Quadrant I|Quadrant II|Quadrant III|Quadrant IV</t>
-        </is>
-      </c>
+          <t>algebra</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
@@ -4129,44 +3673,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>angle8</t>
+          <t>angle9</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Substitute and simplify.</t>
+          <t>Interpret 'Half as Steep'</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Substitute $$\cos\alpha$$ into the formula and simplify, choosing the correct sign.</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>$$-\frac{\sqrt{17}}{17}$$</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
+          <t>Given the context of half-angle formulas, 'half as steep' implies the new angle is `$$\frac{\theta}{2}$$`.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>s4</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -4179,33 +3711,49 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>angle8</t>
+          <t>angle9</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>$$tan(\frac{α}{2})$$</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>Choose Formula</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Which half-angle formula for tangent should be used?</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>$$-4$$</t>
+          <t>$$\tan\left(\frac{\theta}{2}\right) = \frac{1-\cos\theta}{\sin\theta}$$</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
+          <t>mc</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>$$\tan\left(\frac{\theta}{2}\right) = \frac{1-\cos\theta}{\sin\theta}$$|$$\tan\left(\frac{\theta}{2}\right) = \frac{\sin\theta}{1+\cos\theta}$$|$$\tan\left(\frac{\theta}{2}\right) = \pm\sqrt{\frac{1-\cos\theta}{1+\cos\theta}}$$|$$\tan\left(\frac{\theta}{2}\right) = \frac{1}{2}\tan\theta$$</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
@@ -4217,7 +3765,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>angle8</t>
+          <t>angle9</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4227,22 +3775,26 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Recall a half-angle formula for tangent.</t>
+          <t>Find Sine and Cosine</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>You can use $$\tan\left(\frac{\alpha}{2}\right) = \frac{1-\cos\alpha}{\sin\alpha}$$ or $$\tan\left(\frac{\alpha}{2}\right) = \frac{\sin\alpha}{1+\cos\alpha}$$ or $$\tan\left(\frac{\alpha}{2}\right) = \frac{\sin(\alpha/2)}{\cos(\alpha/2)}$$.</t>
+          <t>Given `$$\tan\theta = \frac{5}{3}$$`, construct a right triangle or use identities to find `$$\sin\theta$$` and `$$\cos\theta$$`.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
           <t>h1</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
@@ -4255,7 +3807,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>angle8</t>
+          <t>angle9</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4265,32 +3817,32 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>What is a half-angle formula for tangent?</t>
+          <t>Calculate Sine and Cosine</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>What is one of the half-angle formulas for tangent?</t>
+          <t>Given `$$\tan\theta = \frac{5}{3}$$`, what are the exact values of `$$\sin\theta$$` and `$$\cos\theta$$`?</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>$$\tan\left(\frac{\alpha}{2}\right) = \frac{1-\cos\alpha}{\sin\alpha}$$</t>
+          <t>$$\sin\theta = \frac{5}{\sqrt{34}}, \cos\theta = \frac{3}{\sqrt{34}}$$`</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>algebraic</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>h1</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -4305,7 +3857,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>angle8</t>
+          <t>angle9</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4315,24 +3867,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Determine $$\sin\alpha$$ and $$\cos\alpha$$.</t>
+          <t>Substitute and Solve</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Use the given $$\tan\alpha$$ and quadrant information to find $$\sin\alpha$$ and $$\cos\alpha$$.</t>
+          <t>Substitute the values of `$$\sin\theta$$` and `$$\cos\theta$$` into the half-angle formula for tangent, then use the inverse tangent function to find the angle.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
           <t>h2</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>h1</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -4347,7 +3899,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>angle8</t>
+          <t>angle9</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4357,32 +3909,32 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>What is $$\sin\alpha$$?</t>
+          <t>Calculate `$$\tan\left(\frac{\theta}{2}\right)$$`</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Given $$\tan\alpha=\frac{8}{15}$$ and $$\alpha$$ is in QIII, what is $$\sin\alpha$$?</t>
+          <t>Substitute `$$\sin\theta = \frac{5}{\sqrt{34}}$$` and `$$\cos\theta = \frac{3}{\sqrt{34}}$$` into `$$\tan\left(\frac{\theta}{2}\right) = \frac{1-\cos\theta}{\sin\theta}$$` and simplify.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>$$-\frac{8}{17}$$</t>
+          <t>$$\frac{\sqrt{34}-3}{5}$$`</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>s3</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>h3</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -4394,642 +3946,6 @@
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>angle8</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>What is $$\cos\alpha$$?</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Given $$\tan\alpha=\frac{8}{15}$$ and $$\alpha$$ is in QIII, what is $$\cos\alpha$$?</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>$$-\frac{15}{17}$$</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>angle8</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Substitute and simplify.</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Substitute $$\sin\alpha$$ and $$\cos\alpha$$ into the chosen formula and simplify.</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>angle8</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Substitute and simplify.</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Substitute the values of $$\sin\alpha$$ and $$\cos\alpha$$ into the formula and simplify.</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>$$-4$$</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>s4</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>angle9</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>problem</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Finding the Measurement of a Half Angle</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-3-double-angle-half-angle-and-reduction-formulas</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>angle9</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Now, we will return to the problem posed at the beginning of the section. A bicycle ramp is constructed for high-level competition with an angle of $$\theta$$ formed by the ramp and the ground. Another ramp is to be constructed half as steep for novice competition. If $$\tan\theta=\frac{5}{3}$$ for higher-level competition, what is the measurement of the angle for novice competition?</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>$$\arctan\left(\frac{\sqrt{34}-3}{5}\right)$$</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>angle9</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Interpret "half as steep".</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Given the context of half-angle formulas, "half as steep" refers to the angle itself being halved, i.e., $$\frac{\theta}{2}$$.</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>angle9</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>What is the angle for novice competition?</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>What is the angle for novice competition in terms of $$\theta$$?</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>$$\frac{\theta}{2}$$</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>s1</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>angle9</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Recall a half-angle formula for tangent.</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Recall that $$\tan\left(\frac{\theta}{2}\right) = \frac{1-\cos\theta}{\sin\theta}$$.</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>angle9</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>What is a half-angle formula for tangent?</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>What is one of the half-angle formulas for tangent?</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>$$\tan\left(\frac{\theta}{2}\right) = \frac{1-\cos\theta}{\sin\theta}$$</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>angle9</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Determine $$\sin\theta$$ and $$\cos\theta$$.</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Use the given $$\tan\theta=\frac{5}{3}$$ to find $$\sin\theta$$ and $$\cos\theta$$. Assume $$\theta$$ is in Quadrant I (since it's a ramp angle).</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>angle9</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>What is $$\sin\theta$$?</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Given $$\tan\theta=\frac{5}{3}$$ and $$\theta$$ is in QI, what is $$\sin\theta$$?</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>$$\frac{5}{\sqrt{34}}$$</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>angle9</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>What is $$\cos\theta$$?</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Given $$\tan\theta=\frac{5}{3}$$ and $$\theta$$ is in QI, what is $$\cos\theta$$?</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>$$\frac{3}{\sqrt{34}}$$</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>s4</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>angle9</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Substitute and simplify $$\tan(\frac{\theta}{2})$$.</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Substitute $$\sin\theta$$ and $$\cos\theta$$ into the formula for $$\tan(\frac{\theta}{2})$$ and simplify.</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>$$\frac{\sqrt{34}-3}{5}$$</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>s5</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>angle9</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Express the angle.</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>If $$\tan(\frac{\theta}{2}) = X$$, then $$\frac{\theta}{2} = \arctan(X)$$. What is the final expression for the angle?</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>$$\arctan\left(\frac{\sqrt{34}-3}{5}\right)$$</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>s6</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
